--- a/events/Montemor_2017_WC/Montemor_2017_WC_Results.xlsx
+++ b/events/Montemor_2017_WC/Montemor_2017_WC_Results.xlsx
@@ -2716,6 +2716,11 @@
           <t>00:02.224</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7034,6 +7039,11 @@
           <t>01:54.176</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8493,6 +8503,11 @@
           <t>00:00.880</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -16314,6 +16329,11 @@
           <t>00:04.550</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -25352,6 +25372,11 @@
       <c r="Q357" t="inlineStr">
         <is>
           <t>00:00.792</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>42444</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36919,6 +36944,28 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Montemor_2017_WC/Montemor_2017_WC_Results.xlsx
+++ b/events/Montemor_2017_WC/Montemor_2017_WC_Results.xlsx
@@ -1006,6 +1006,11 @@
       <c r="L8" t="n">
         <v>8</v>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>60677</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -1901,6 +1906,11 @@
           <t>00:00.028</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>54273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2036,6 +2046,11 @@
           <t>00:12.376</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3066,6 +3081,11 @@
           <t>00:36.988</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3891,6 +3911,11 @@
           <t>54676</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4015,6 +4040,16 @@
       <c r="L52" t="n">
         <v>3</v>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>41999</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>71786</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -4364,6 +4399,11 @@
       <c r="L57" t="n">
         <v>6</v>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>48802</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>47895</t>
@@ -4439,6 +4479,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4509,6 +4554,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4939,6 +4989,11 @@
           <t>00:04.008</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>53227</t>
@@ -5229,6 +5284,16 @@
           <t>00:01.588</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6774,6 +6839,11 @@
           <t>04:22.352</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7734,6 +7804,11 @@
           <t>54676</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8853,6 +8928,11 @@
           <t>00:17.056</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11651,6 +11731,11 @@
           <t>00:03.052</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11700,6 +11785,11 @@
       <c r="L163" t="n">
         <v>6</v>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>60677</t>
+        </is>
+      </c>
       <c r="X163" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -11990,6 +12080,11 @@
           <t>00:08.152</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>75511</t>
+        </is>
+      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>60129</t>
@@ -12985,6 +13080,11 @@
           <t>00:02.424</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13244,6 +13344,11 @@
       <c r="L185" t="n">
         <v>2</v>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>60677</t>
+        </is>
+      </c>
       <c r="X185" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -14652,6 +14757,11 @@
           <t>00:15.668</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15645,6 +15755,11 @@
           <t>00:17.226</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15851,6 +15966,11 @@
           <t>00:19.631</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>54273</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17614,6 +17734,11 @@
           <t>54676</t>
         </is>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17984,6 +18109,11 @@
           <t>03:09.732</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>53227</t>
@@ -18138,6 +18268,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18210,6 +18345,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19098,6 +19238,16 @@
           <t>00:10.010</t>
         </is>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -19781,6 +19931,11 @@
           <t>00:09.641</t>
         </is>
       </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -21209,6 +21364,11 @@
           <t>00:01.896</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -21398,6 +21558,11 @@
           <t>01:46.206</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>75511</t>
+        </is>
+      </c>
       <c r="S301" t="inlineStr">
         <is>
           <t>60129</t>
@@ -22442,6 +22607,11 @@
           <t>00:01.068</t>
         </is>
       </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -22932,6 +23102,11 @@
           <t>00:01.665</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -23210,6 +23385,11 @@
           <t>00:00.302</t>
         </is>
       </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -24017,6 +24197,11 @@
           <t>00:02.873</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>75511</t>
+        </is>
+      </c>
       <c r="S338" t="inlineStr">
         <is>
           <t>60129</t>
@@ -24469,6 +24654,11 @@
           <t>00:09.079</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
       <c r="S344" t="inlineStr">
         <is>
           <t>61287</t>
@@ -24608,6 +24798,11 @@
           <t>00:00.176</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -27318,6 +27513,11 @@
           <t>00:05.464</t>
         </is>
       </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>75511</t>
+        </is>
+      </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>60129</t>
@@ -28562,6 +28762,16 @@
           <t>00:00.772</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -29301,6 +29511,11 @@
           <t>00:38.764</t>
         </is>
       </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>75664</t>
+        </is>
+      </c>
       <c r="S411" t="inlineStr">
         <is>
           <t>75663</t>
@@ -29500,6 +29715,11 @@
           <t>01:20.586</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
           <t>53227</t>
@@ -29592,6 +29812,11 @@
           <t>54773</t>
         </is>
       </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="U415" t="inlineStr">
         <is>
           <t>36450</t>
@@ -29940,6 +30165,11 @@
           <t>54676</t>
         </is>
       </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -30703,6 +30933,11 @@
           <t>54844</t>
         </is>
       </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
       <c r="U428" t="inlineStr">
         <is>
           <t>49452</t>
@@ -30877,6 +31112,11 @@
           <t>64766</t>
         </is>
       </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -31910,6 +32150,11 @@
           <t>20:24.200</t>
         </is>
       </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -32476,6 +32721,11 @@
           <t>01:22.550</t>
         </is>
       </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -32948,6 +33198,11 @@
       <c r="L460" t="n">
         <v>14</v>
       </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
       <c r="X460" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -33373,6 +33628,11 @@
       <c r="Q466" t="inlineStr">
         <is>
           <t>00:42.660</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>36459</t>
         </is>
       </c>
     </row>
@@ -33443,7 +33703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36966,6 +37226,446 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Janne</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MAENTYNEN</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>41999</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tarmo</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AALTO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>48802</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Edmond</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SANKA</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Kyrylo</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CHERNOMOROV</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>54273</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Balazs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Combe</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SECK</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Raquel</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DA COSTA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>60677</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Juan Pablo</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Mate</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>GYORGJAKAB</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>71786</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Joona</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>MAENTYNEN</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>75511</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Diexe</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MOLINA ZULUAGA</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>75664</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>RODRIGUES</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
